--- a/src/CRB-MARSHAL/inputs/Simulations_ID.xlsx
+++ b/src/CRB-MARSHAL/inputs/Simulations_ID.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdagostino\Desktop\GITHUB\TRoot\src\CRB-MARSHAL\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EF87B41-77E3-4D1A-81ED-A6FE9AC61015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73407431-DC54-4EF5-9C54-320F396EE8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="15">
   <si>
     <t>Scenario_ID</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>3_60</t>
+  </si>
+  <si>
+    <t>SG_timing_1</t>
+  </si>
+  <si>
+    <t>SG_timing_2</t>
   </si>
 </sst>
 </file>
@@ -382,14 +388,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.140625" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -399,8 +407,14 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -410,8 +424,14 @@
       <c r="C2">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -421,8 +441,14 @@
       <c r="C3">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -432,8 +458,14 @@
       <c r="C4">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>7</v>
+      </c>
+      <c r="E4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -443,8 +475,14 @@
       <c r="C5">
         <v>30</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>7</v>
+      </c>
+      <c r="E5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -454,8 +492,14 @@
       <c r="C6">
         <v>60</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>7</v>
+      </c>
+      <c r="E6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -465,8 +509,14 @@
       <c r="C7">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -476,8 +526,14 @@
       <c r="C8">
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -485,6 +541,12 @@
         <v>3</v>
       </c>
       <c r="C9">
+        <v>60</v>
+      </c>
+      <c r="D9">
+        <v>7</v>
+      </c>
+      <c r="E9">
         <v>60</v>
       </c>
     </row>

--- a/src/CRB-MARSHAL/inputs/Simulations_ID.xlsx
+++ b/src/CRB-MARSHAL/inputs/Simulations_ID.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mdagostino\Desktop\GITHUB\TRoot\src\CRB-MARSHAL\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73407431-DC54-4EF5-9C54-320F396EE8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF46C9D-A1DA-464D-A9B9-0AC190DAC1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -389,15 +389,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.85546875" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.140625" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -414,7 +414,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -431,7 +431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -448,7 +448,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -465,7 +465,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -482,7 +482,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -496,10 +496,10 @@
         <v>7</v>
       </c>
       <c r="E6">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -513,10 +513,10 @@
         <v>7</v>
       </c>
       <c r="E7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -530,10 +530,10 @@
         <v>7</v>
       </c>
       <c r="E8">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
